--- a/db/A7XLK-3215-番茄村.xlsx
+++ b/db/A7XLK-3215-番茄村.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou/db/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaichung/Documents/7_WebSite/7.11_CommunityWebSite/A7Xinlinkou4/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0848C19-ABBE-A04F-8A17-03FE1F75AB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567529BF-D455-6045-9F82-B9F93BF6B26E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="39840" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2020" yWindow="500" windowWidth="39840" windowHeight="22540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Transformed by JSON-CSV.CO" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="246">
   <si>
     <t>id</t>
   </si>
@@ -2610,6 +2610,159 @@
   </si>
   <si>
     <t>fig/XLK-321-RestaurantA7/AiCity-953-番茄村-934.jpg</t>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日式梅醬豬排堡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-321-RestaurantA7/AiCity-953-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>番茄村</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-605.jpg</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>京都壽喜牛起司蛋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-321-RestaurantA7/AiCity-953-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>番茄村</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-105.jpg</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日式胡麻雞排堡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-321-RestaurantA7/AiCity-953-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>番茄村</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-106.jpg</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日式胡麻雞排蛋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-321-RestaurantA7/AiCity-953-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>番茄村</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-205.jpg</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>厚片-爆量梅醬起司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>京都壽喜牛炒麵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fig/XLK-321-RestaurantA7/AiCity-953-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="PMingLiU"/>
+        <family val="1"/>
+        <charset val="136"/>
+      </rPr>
+      <t>番茄村</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-914.jpg</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3024,7 +3177,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="9"/>
@@ -3032,7 +3185,7 @@
     <col min="3" max="3" width="35" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" style="9"/>
     <col min="5" max="5" width="8.83203125" style="1"/>
-    <col min="6" max="6" width="39" style="1" customWidth="1"/>
+    <col min="6" max="6" width="67" style="1" customWidth="1"/>
     <col min="7" max="7" width="18" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="8.83203125" style="1"/>
@@ -3328,68 +3481,65 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="9">
-        <v>201</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>8</v>
+        <v>105</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>237</v>
       </c>
       <c r="D13" s="10">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>19</v>
+        <v>238</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="9">
-        <v>201</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>13</v>
+        <v>106</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="D14" s="10">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>19</v>
+        <v>240</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="9">
-        <v>202</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>10</v>
+        <v>201</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D15" s="10">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E15" s="1">
         <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>19</v>
@@ -3400,22 +3550,19 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="9">
-        <v>202</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>10</v>
+        <v>201</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D16" s="10">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E16" s="1">
         <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>19</v>
@@ -3432,10 +3579,10 @@
         <v>10</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D17" s="10">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
@@ -3452,19 +3599,22 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="9">
-        <v>203</v>
+        <v>202</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D18" s="10">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>19</v>
@@ -3475,10 +3625,13 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="9">
-        <v>203</v>
+        <v>202</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D19" s="10">
         <v>59</v>
@@ -3487,7 +3640,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>19</v>
@@ -3501,10 +3654,10 @@
         <v>203</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D20" s="10">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
@@ -3521,22 +3674,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="9">
-        <v>204</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>10</v>
+        <v>203</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D21" s="10">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>19</v>
@@ -3547,22 +3697,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="9">
-        <v>204</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>10</v>
+        <v>203</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D22" s="10">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E22" s="1">
         <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>19</v>
@@ -3579,10 +3726,10 @@
         <v>10</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D23" s="10">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
@@ -3599,22 +3746,25 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="9">
-        <v>301</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>25</v>
+        <v>204</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="D24" s="10">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>24</v>
+        <v>174</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>67</v>
@@ -3622,22 +3772,25 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="9">
-        <v>301</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>27</v>
+        <v>204</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D25" s="10">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>67</v>
@@ -3645,22 +3798,25 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="9">
-        <v>301</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>29</v>
+        <v>205</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="D26" s="10">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>67</v>
@@ -3670,8 +3826,8 @@
       <c r="A27" s="9">
         <v>301</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>31</v>
+      <c r="C27" s="8" t="s">
+        <v>25</v>
       </c>
       <c r="D27" s="10">
         <v>25</v>
@@ -3682,7 +3838,7 @@
       <c r="F27" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="8" t="s">
         <v>24</v>
       </c>
       <c r="H27" s="1" t="s">
@@ -3691,19 +3847,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="9">
-        <v>302</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>26</v>
+        <v>301</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="D28" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G28" s="7" t="s">
         <v>24</v>
@@ -3714,19 +3870,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="9">
-        <v>302</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>28</v>
+        <v>301</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D29" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>24</v>
@@ -3737,19 +3893,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="9">
-        <v>302</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>30</v>
+        <v>301</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="D30" s="10">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E30" s="1">
         <v>0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G30" s="7" t="s">
         <v>24</v>
@@ -3763,7 +3919,7 @@
         <v>302</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D31" s="10">
         <v>30</v>
@@ -3783,117 +3939,111 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="9">
-        <v>401</v>
+        <v>302</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D32" s="10">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E32" s="1">
         <v>0</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>33</v>
+        <v>176</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="9">
-        <v>401</v>
+        <v>302</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>165</v>
+        <v>30</v>
       </c>
       <c r="D33" s="10">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E33" s="1">
         <v>0</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>33</v>
+        <v>176</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="9">
-        <v>401</v>
+        <v>302</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D34" s="9">
-        <v>50</v>
+        <v>32</v>
+      </c>
+      <c r="D34" s="10">
+        <v>30</v>
       </c>
       <c r="E34" s="1">
         <v>0</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>33</v>
+        <v>176</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="9">
-        <v>402</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D35" s="9">
-        <v>45</v>
+        <v>303</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D35" s="10">
+        <v>49</v>
       </c>
       <c r="E35" s="1">
         <v>0</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>33</v>
+        <v>176</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="9">
-        <v>402</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="D36" s="9">
-        <v>55</v>
+        <v>401</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="10">
+        <v>40</v>
       </c>
       <c r="E36" s="1">
         <v>0</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>33</v>
@@ -3904,22 +4054,19 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="9">
-        <v>402</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D37" s="9">
-        <v>55</v>
+        <v>401</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" s="10">
+        <v>50</v>
       </c>
       <c r="E37" s="1">
         <v>0</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>33</v>
@@ -3929,20 +4076,20 @@
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="1">
-        <v>403</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>35</v>
+      <c r="A38" s="9">
+        <v>401</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="D38" s="9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E38" s="1">
         <v>0</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>33</v>
@@ -3953,19 +4100,22 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="9">
-        <v>403</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>39</v>
+        <v>402</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="D39" s="9">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="E39" s="1">
         <v>0</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>33</v>
@@ -3976,19 +4126,22 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="9">
-        <v>403</v>
+        <v>402</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="D40" s="9">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E40" s="1">
         <v>0</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>33</v>
@@ -3999,19 +4152,22 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="9">
-        <v>404</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>36</v>
+        <v>402</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="D41" s="9">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="E41" s="1">
         <v>0</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>33</v>
@@ -4021,20 +4177,20 @@
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="9">
-        <v>404</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>40</v>
+      <c r="A42" s="1">
+        <v>403</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D42" s="9">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="E42" s="1">
         <v>0</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>33</v>
@@ -4045,19 +4201,19 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="9">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="D43" s="9">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E43" s="1">
         <v>0</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>33</v>
@@ -4068,22 +4224,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="9">
-        <v>405</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>37</v>
+        <v>403</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="D44" s="9">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E44" s="1">
         <v>0</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>33</v>
@@ -4094,22 +4247,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="9">
-        <v>405</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>58</v>
+        <v>404</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D45" s="9">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E45" s="1">
         <v>0</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>33</v>
@@ -4120,13 +4270,10 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="9">
-        <v>405</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>10</v>
+        <v>404</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D46" s="9">
         <v>80</v>
@@ -4135,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>33</v>
@@ -4146,117 +4293,120 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="9">
-        <v>501</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>47</v>
+        <v>404</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="D47" s="9">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>43</v>
+        <v>180</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="9">
-        <v>501</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>49</v>
+        <v>405</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D48" s="9">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>43</v>
+        <v>181</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="9">
-        <v>502</v>
+        <v>405</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>44</v>
+      <c r="C49" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="D49" s="9">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E49" s="1">
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>43</v>
+        <v>181</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="9">
-        <v>502</v>
+        <v>405</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D50" s="9">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E50" s="1">
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>43</v>
+        <v>181</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="9">
-        <v>503</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>45</v>
+        <v>501</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D51" s="9">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E51" s="1">
         <v>0</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>43</v>
@@ -4267,19 +4417,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="9">
-        <v>503</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>51</v>
+        <v>501</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="D52" s="9">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="E52" s="1">
         <v>0</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>43</v>
@@ -4290,22 +4440,22 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="9">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D53" s="9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E53" s="1">
         <v>0</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>43</v>
@@ -4316,22 +4466,22 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="9">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>52</v>
+      <c r="C54" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="D54" s="9">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E54" s="1">
         <v>0</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>43</v>
@@ -4342,126 +4492,123 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="9">
-        <v>601</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>55</v>
+        <v>503</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="D55" s="9">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E55" s="1">
         <v>0</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>53</v>
+        <v>184</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="9">
-        <v>602</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>54</v>
+        <v>503</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>51</v>
       </c>
       <c r="D56" s="9">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E56" s="1">
         <v>0</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>53</v>
+        <v>184</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="9">
-        <v>603</v>
+        <v>504</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>57</v>
+      <c r="C57" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D57" s="9">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E57" s="1">
         <v>0</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="9">
-        <v>603</v>
+        <v>504</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D58" s="9">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E58" s="1">
         <v>0</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="9">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>61</v>
+      <c r="C59" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="D59" s="9">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>56</v>
+        <v>186</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>66</v>
@@ -4469,22 +4616,22 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="9">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D60" s="9">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="E60" s="1">
         <v>0</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>62</v>
+        <v>187</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>66</v>
@@ -4492,22 +4639,25 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="9">
-        <v>604</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>64</v>
+        <v>605</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D61" s="9">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E61" s="1">
         <v>0</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>62</v>
+        <v>236</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>66</v>
@@ -4515,134 +4665,143 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="9">
-        <v>701</v>
+        <v>603</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D62" s="9">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E62" s="1">
         <v>0</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="9">
-        <v>701</v>
+        <v>603</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="D63" s="9">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E63" s="1">
         <v>0</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="9">
-        <v>702</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>69</v>
+        <v>603</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="D64" s="9">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E64" s="1">
         <v>0</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="9">
-        <v>702</v>
-      </c>
-      <c r="C65" s="11" t="s">
-        <v>77</v>
+        <v>604</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="D65" s="9">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="E65" s="1">
         <v>0</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="9">
-        <v>702.5</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>70</v>
+        <v>604</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="D66" s="9">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="E66" s="1">
         <v>0</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="9">
-        <v>702.9</v>
-      </c>
-      <c r="C67" s="11" t="s">
-        <v>78</v>
+        <v>701</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="D67" s="9">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E67" s="1">
         <v>0</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>68</v>
@@ -4653,13 +4812,10 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="9">
-        <v>703.7</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>71</v>
+        <v>701</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>76</v>
       </c>
       <c r="D68" s="9">
         <v>35</v>
@@ -4668,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>68</v>
@@ -4679,22 +4835,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="9">
-        <v>704.1</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="11" t="s">
-        <v>79</v>
+        <v>702</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="D69" s="9">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E69" s="1">
         <v>0</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>68</v>
@@ -4705,19 +4858,19 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="9">
-        <v>704.5</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>72</v>
+        <v>702</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="D70" s="9">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E70" s="1">
         <v>0</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>68</v>
@@ -4728,19 +4881,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="9">
-        <v>704.9</v>
-      </c>
-      <c r="C71" s="11" t="s">
-        <v>80</v>
+        <v>702.5</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="D71" s="9">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E71" s="1">
         <v>0</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>68</v>
@@ -4751,19 +4904,19 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="9">
-        <v>706</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>73</v>
+        <v>702.9</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>78</v>
       </c>
       <c r="D72" s="9">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E72" s="1">
         <v>0</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>68</v>
@@ -4774,19 +4927,22 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="9">
-        <v>706</v>
-      </c>
-      <c r="C73" s="11" t="s">
-        <v>81</v>
+        <v>703.7</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="D73" s="9">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E73" s="1">
         <v>0</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>68</v>
@@ -4797,22 +4953,22 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="9">
-        <v>707</v>
+        <v>704.1</v>
       </c>
       <c r="B74" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>74</v>
+      <c r="C74" s="11" t="s">
+        <v>79</v>
       </c>
       <c r="D74" s="9">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E74" s="1">
         <v>0</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>68</v>
@@ -4823,22 +4979,19 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="9">
-        <v>707</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C75" s="11" t="s">
-        <v>82</v>
+        <v>704.5</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="D75" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E75" s="1">
         <v>0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>68</v>
@@ -4849,137 +5002,140 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="9">
-        <v>801</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>94</v>
+        <v>704.9</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="D76" s="9">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E76" s="1">
         <v>0</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="9">
-        <v>802</v>
+        <v>706</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D77" s="9">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E77" s="1">
         <v>0</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="9">
-        <v>803</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>85</v>
+        <v>706</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>81</v>
       </c>
       <c r="D78" s="9">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E78" s="1">
         <v>0</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="9">
-        <v>804</v>
+        <v>707</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="D79" s="9">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E79" s="1">
         <v>0</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="9">
-        <v>805</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>87</v>
+        <v>707</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="D80" s="9">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E80" s="1">
         <v>0</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="9">
-        <v>806</v>
-      </c>
-      <c r="B81" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D81" s="9">
         <v>10</v>
       </c>
-      <c r="C81" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D81" s="9">
-        <v>30</v>
-      </c>
       <c r="E81" s="1">
         <v>0</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>83</v>
@@ -4990,22 +5146,19 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="9">
-        <v>806</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>89</v>
+        <v>802</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="D82" s="9">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E82" s="1">
         <v>0</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>83</v>
@@ -5016,10 +5169,10 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="9">
-        <v>807</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>90</v>
+        <v>803</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="D83" s="9">
         <v>35</v>
@@ -5028,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>83</v>
@@ -5039,19 +5192,19 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="9">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D84" s="9">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E84" s="1">
         <v>0</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>83</v>
@@ -5062,22 +5215,19 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="9">
-        <v>809</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>10</v>
+        <v>805</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D85" s="9">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E85" s="1">
         <v>0</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>83</v>
@@ -5088,19 +5238,22 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="9">
-        <v>810</v>
+        <v>806</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D86" s="9">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E86" s="1">
         <v>0</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>83</v>
@@ -5111,140 +5264,143 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="9">
-        <v>901</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>101</v>
+        <v>806</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>89</v>
       </c>
       <c r="D87" s="9">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="E87" s="1">
         <v>0</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>96</v>
+        <v>202</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="9">
-        <v>902</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>102</v>
+        <v>807</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="D88" s="9">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="E88" s="1">
         <v>0</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>96</v>
+        <v>203</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="9">
-        <v>903</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>103</v>
+        <v>808</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="D89" s="9">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="E89" s="1">
         <v>0</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>96</v>
+        <v>204</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="9">
-        <v>904</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>104</v>
+        <v>809</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="D90" s="9">
-        <v>99</v>
+        <v>45</v>
       </c>
       <c r="E90" s="1">
         <v>0</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>96</v>
+        <v>205</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="9">
-        <v>905</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>105</v>
+        <v>810</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="D91" s="9">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="E91" s="1">
         <v>0</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>96</v>
+        <v>206</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="9">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D92" s="9">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E92" s="1">
         <v>0</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>95</v>
@@ -5252,22 +5408,22 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="9">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D93" s="9">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E93" s="1">
         <v>0</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>95</v>
@@ -5275,25 +5431,25 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="9">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D94" s="9">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="E94" s="1">
         <v>0</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>95</v>
@@ -5301,25 +5457,22 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="9">
-        <v>907</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>10</v>
+        <v>904</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="D95" s="9">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="E95" s="1">
         <v>0</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>95</v>
@@ -5327,22 +5480,22 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="9">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D96" s="9">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="E96" s="1">
         <v>0</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>95</v>
@@ -5350,22 +5503,22 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="9">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D97" s="9">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E97" s="1">
         <v>0</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>95</v>
@@ -5373,22 +5526,22 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="9">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D98" s="9">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="E98" s="1">
         <v>0</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>95</v>
@@ -5396,22 +5549,25 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="9">
-        <v>911</v>
+        <v>907</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D99" s="9">
-        <v>139</v>
+        <v>70</v>
       </c>
       <c r="E99" s="1">
         <v>0</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>95</v>
@@ -5419,22 +5575,25 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="9">
-        <v>912</v>
+        <v>907</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D100" s="9">
-        <v>139</v>
+        <v>80</v>
       </c>
       <c r="E100" s="1">
         <v>0</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>100</v>
+        <v>213</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>95</v>
@@ -5442,22 +5601,25 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="9">
-        <v>913</v>
+        <v>914</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>113</v>
+        <v>244</v>
       </c>
       <c r="D101" s="9">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="E101" s="1">
         <v>0</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G101" s="8" t="s">
-        <v>100</v>
+        <v>245</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>95</v>
@@ -5465,166 +5627,157 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="9">
-        <v>1001</v>
-      </c>
-      <c r="C102" s="12" t="s">
-        <v>119</v>
+        <v>908</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="D102" s="9">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="E102" s="1">
         <v>0</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>163</v>
+        <v>98</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="9">
-        <v>1001</v>
-      </c>
-      <c r="C103" s="12" t="s">
-        <v>120</v>
+        <v>909</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="D103" s="9">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="E103" s="1">
         <v>0</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>163</v>
+        <v>98</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="9">
-        <v>1001</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>121</v>
+        <v>910</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>110</v>
       </c>
       <c r="D104" s="9">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="E104" s="1">
         <v>0</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>163</v>
+        <v>99</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="9">
-        <v>1001</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>122</v>
+        <v>911</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>111</v>
       </c>
       <c r="D105" s="9">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="E105" s="1">
         <v>0</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>163</v>
+        <v>99</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="9">
-        <v>1002</v>
-      </c>
-      <c r="B106" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>123</v>
+        <v>912</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="D106" s="9">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="E106" s="1">
         <v>0</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>163</v>
+        <v>218</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="9">
-        <v>1002</v>
-      </c>
-      <c r="B107" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C107" s="12" t="s">
-        <v>124</v>
+        <v>913</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="D107" s="9">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="E107" s="1">
         <v>0</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="G107" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>163</v>
+        <v>219</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="9">
-        <v>1002</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>10</v>
+        <v>1001</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D108" s="9">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E108" s="1">
         <v>0</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G108" s="7" t="s">
         <v>116</v>
@@ -5635,22 +5788,19 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="9">
-        <v>1002</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>10</v>
+        <v>1001</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D109" s="9">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E109" s="1">
         <v>0</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G109" s="7" t="s">
         <v>116</v>
@@ -5661,25 +5811,22 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="9">
-        <v>1003</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>10</v>
+        <v>1001</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D110" s="9">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E110" s="1">
         <v>0</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>163</v>
@@ -5687,25 +5834,22 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="9">
-        <v>1003</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>10</v>
+        <v>1001</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D111" s="9">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E111" s="1">
         <v>0</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>163</v>
@@ -5713,25 +5857,25 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="9">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D112" s="9">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E112" s="1">
         <v>0</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>163</v>
@@ -5739,25 +5883,25 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="9">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D113" s="9">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E113" s="1">
         <v>0</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>163</v>
@@ -5765,25 +5909,25 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="9">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B114" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D114" s="9">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E114" s="1">
         <v>0</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>163</v>
@@ -5791,25 +5935,25 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="9">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D115" s="9">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E115" s="1">
         <v>0</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>163</v>
@@ -5817,10 +5961,13 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="9">
-        <v>1004</v>
+        <v>1003</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D116" s="9">
         <v>20</v>
@@ -5829,7 +5976,7 @@
         <v>0</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G116" s="7" t="s">
         <v>117</v>
@@ -5840,10 +5987,13 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="9">
-        <v>1004</v>
+        <v>1003</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D117" s="9">
         <v>20</v>
@@ -5852,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G117" s="7" t="s">
         <v>117</v>
@@ -5863,10 +6013,13 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="9">
-        <v>1004</v>
+        <v>1003</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D118" s="9">
         <v>25</v>
@@ -5875,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G118" s="7" t="s">
         <v>117</v>
@@ -5886,10 +6039,13 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="9">
-        <v>1004</v>
+        <v>1003</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D119" s="9">
         <v>25</v>
@@ -5898,7 +6054,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G119" s="7" t="s">
         <v>117</v>
@@ -5909,10 +6065,13 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="9">
-        <v>1004</v>
+        <v>1003</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D120" s="9">
         <v>30</v>
@@ -5921,7 +6080,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G120" s="7" t="s">
         <v>117</v>
@@ -5932,10 +6091,13 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="9">
-        <v>1004</v>
+        <v>1003</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D121" s="9">
         <v>30</v>
@@ -5944,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G121" s="7" t="s">
         <v>117</v>
@@ -5955,22 +6117,22 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="9">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D122" s="9">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="E122" s="1">
         <v>0</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G122" s="8" t="s">
-        <v>127</v>
+        <v>223</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>163</v>
@@ -5978,33 +6140,33 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="9">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D123" s="9">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E123" s="1">
         <v>0</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="9">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D124" s="9">
         <v>25</v>
@@ -6013,44 +6175,44 @@
         <v>0</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H124" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="9">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D125" s="9">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E125" s="1">
         <v>0</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="9">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D126" s="9">
         <v>30</v>
@@ -6059,24 +6221,21 @@
         <v>0</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H126" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="9">
-        <v>1007</v>
-      </c>
-      <c r="B127" s="4" t="s">
-        <v>10</v>
+        <v>1004</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D127" s="9">
         <v>30</v>
@@ -6085,59 +6244,53 @@
         <v>0</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H127" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="9">
-        <v>1007</v>
-      </c>
-      <c r="B128" s="4" t="s">
-        <v>10</v>
+        <v>1005</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="D128" s="9">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E128" s="1">
         <v>0</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G128" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="H128" s="7" t="s">
-        <v>118</v>
+        <v>224</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="9">
-        <v>1008</v>
-      </c>
-      <c r="B129" s="4" t="s">
-        <v>10</v>
+        <v>1006</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D129" s="9">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E129" s="1">
         <v>0</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G129" s="7" t="s">
         <v>118</v>
@@ -6148,22 +6301,19 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="9">
-        <v>1008</v>
-      </c>
-      <c r="B130" s="4" t="s">
-        <v>10</v>
+        <v>1006</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D130" s="9">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E130" s="1">
         <v>0</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G130" s="7" t="s">
         <v>118</v>
@@ -6174,22 +6324,19 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="9">
-        <v>1008</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>10</v>
+        <v>1006</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="D131" s="9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E131" s="1">
         <v>0</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G131" s="7" t="s">
         <v>118</v>
@@ -6200,22 +6347,19 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="9">
-        <v>1008</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>10</v>
+        <v>1006</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D132" s="9">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E132" s="1">
         <v>0</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G132" s="7" t="s">
         <v>118</v>
@@ -6226,19 +6370,22 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="9">
-        <v>1009</v>
+        <v>1007</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D133" s="9">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E133" s="1">
         <v>0</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G133" s="7" t="s">
         <v>118</v>
@@ -6249,19 +6396,22 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="9">
-        <v>1009</v>
+        <v>1007</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D134" s="9">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E134" s="1">
         <v>0</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G134" s="7" t="s">
         <v>118</v>
@@ -6272,19 +6422,22 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="9">
-        <v>1010</v>
+        <v>1008</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D135" s="9">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E135" s="1">
         <v>0</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G135" s="7" t="s">
         <v>118</v>
@@ -6295,19 +6448,22 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="9">
-        <v>1010</v>
+        <v>1008</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D136" s="9">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E136" s="1">
         <v>0</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G136" s="7" t="s">
         <v>118</v>
@@ -6318,22 +6474,22 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="9">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D137" s="9">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E137" s="1">
         <v>0</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G137" s="7" t="s">
         <v>118</v>
@@ -6344,22 +6500,22 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="9">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="B138" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D138" s="9">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E138" s="1">
         <v>0</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G138" s="7" t="s">
         <v>118</v>
@@ -6370,22 +6526,19 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="9">
-        <v>1012</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>10</v>
+        <v>1009</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D139" s="9">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E139" s="1">
         <v>0</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G139" s="7" t="s">
         <v>118</v>
@@ -6396,13 +6549,10 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="9">
-        <v>1012</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>10</v>
+        <v>1009</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D140" s="9">
         <v>50</v>
@@ -6411,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G140" s="7" t="s">
         <v>118</v>
@@ -6422,10 +6572,10 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="9">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D141" s="9">
         <v>45</v>
@@ -6434,7 +6584,7 @@
         <v>0</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G141" s="7" t="s">
         <v>118</v>
@@ -6445,10 +6595,10 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="9">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D142" s="9">
         <v>50</v>
@@ -6457,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G142" s="7" t="s">
         <v>118</v>
@@ -6468,19 +6618,22 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="9">
-        <v>1014</v>
+        <v>1011</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D143" s="9">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E143" s="1">
         <v>0</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G143" s="7" t="s">
         <v>118</v>
@@ -6491,24 +6644,171 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="9">
-        <v>1014</v>
+        <v>1011</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D144" s="9">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E144" s="1">
         <v>0</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G144" s="7" t="s">
         <v>118</v>
       </c>
       <c r="H144" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="9">
+        <v>1012</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D145" s="9">
+        <v>40</v>
+      </c>
+      <c r="E145" s="1">
+        <v>0</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="9">
+        <v>1012</v>
+      </c>
+      <c r="B146" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D146" s="9">
+        <v>50</v>
+      </c>
+      <c r="E146" s="1">
+        <v>0</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H146" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="9">
+        <v>1013</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D147" s="9">
+        <v>45</v>
+      </c>
+      <c r="E147" s="1">
+        <v>0</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="9">
+        <v>1013</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D148" s="9">
+        <v>50</v>
+      </c>
+      <c r="E148" s="1">
+        <v>0</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="9">
+        <v>1014</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D149" s="9">
+        <v>55</v>
+      </c>
+      <c r="E149" s="1">
+        <v>0</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="9">
+        <v>1014</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D150" s="9">
+        <v>65</v>
+      </c>
+      <c r="E150" s="1">
+        <v>0</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H150" s="7" t="s">
         <v>118</v>
       </c>
     </row>
